--- a/artfynd/A 57388-2025 artfynd.xlsx
+++ b/artfynd/A 57388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>360621</v>
+        <v>63829422</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>O Storbrännan, Vb</t>
+          <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759771.7761577844</v>
+        <v>759635</v>
       </c>
       <c r="R2" t="n">
-        <v>7168744.796954348</v>
+        <v>7168836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +746,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-10-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,37 +760,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>gammal granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Dead wood # Picea abies subsp. abies # död gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesbedömning</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1562168</v>
+        <v>360618</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +825,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Sörbyn, Vb</t>
+          <t>O Storbrännan, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759941.8706078456</v>
+        <v>759779</v>
       </c>
       <c r="R3" t="n">
-        <v>7168880.830556215</v>
+        <v>7168633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +882,9 @@
           <t>2011-10-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +899,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -907,15 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>360620</v>
+        <v>360619</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759787.4527100958</v>
+        <v>759773</v>
       </c>
       <c r="R4" t="n">
-        <v>7168763.861434344</v>
+        <v>7168730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +983,9 @@
           <t>2011-10-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +1000,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1023,50 +1016,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1598039</v>
+        <v>360620</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SV Sörbyn, Vb</t>
+          <t>O Storbrännan, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759940.8394045167</v>
+        <v>759787</v>
       </c>
       <c r="R5" t="n">
-        <v>7168877.716674411</v>
+        <v>7168764</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1084,9 @@
           <t>2011-10-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-10-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1101,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1139,15 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>360619</v>
+        <v>360621</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759773.0630817593</v>
+        <v>759772</v>
       </c>
       <c r="R6" t="n">
-        <v>7168729.779449927</v>
+        <v>7168745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1185,9 @@
           <t>2011-10-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-10-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1202,7 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1255,15 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>63830533</v>
+        <v>63829057</v>
       </c>
       <c r="B7" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759911.0331374415</v>
+        <v>759580</v>
       </c>
       <c r="R7" t="n">
-        <v>7168806.439106487</v>
+        <v>7168828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,19 +1292,9 @@
           <t>2015-10-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-10-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,15 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>63830645</v>
+        <v>63829073</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759890.1905127205</v>
+        <v>759616</v>
       </c>
       <c r="R8" t="n">
-        <v>7168792.117772737</v>
+        <v>7168831</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,19 +1396,9 @@
           <t>2015-10-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-10-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,15 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>63829057</v>
+        <v>63829084</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759579.8470106471</v>
+        <v>759610</v>
       </c>
       <c r="R9" t="n">
-        <v>7168828.19658863</v>
+        <v>7168850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,19 +1500,9 @@
           <t>2015-10-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-10-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,6 +1527,1239 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>63829216</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>759622</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7168831</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>63829739</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>759631</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7168878</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>63829862</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>759655</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7168902</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>63830376</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>759725</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7168866</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>63830533</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>759911</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7168806</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>63830645</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>759890</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7168792</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>63831337</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>760013</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7168716</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113439227</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>760032</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7168798</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1598039</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SV Sörbyn, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>759941</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7168878</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2011-10-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2011-10-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>63830251</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>759724</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7168866</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2015-10-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1858318</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SV Sörbyn, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>759887</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7168694</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2011-10-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2011-10-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1858558</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SV Sörbyn, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>759947</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7168698</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2011-10-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2011-10-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57388-2025 artfynd.xlsx
+++ b/artfynd/A 57388-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/360618</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/360619</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/360620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/360621</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829073</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829084</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829216</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1735,6 +1785,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829739</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1835,6 +1890,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63829862</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1939,6 +1999,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63830376</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63830533</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63830645</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63831337</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2353,6 +2433,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113439227</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,6 +2539,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1598039</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2558,6 +2648,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63830251</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2659,6 +2754,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1858318</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2760,8 +2860,35 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1858558</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>